--- a/results/04_final_refined_daily_hydroclimate_data/601/Dry_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/601/Dry_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -805,8 +805,8 @@
       <c r="C30">
         <v>29</v>
       </c>
-      <c r="D30" t="s">
-        <v>4</v>
+      <c r="D30">
+        <v>18.2</v>
       </c>
     </row>
     <row r="31" spans="1:4">
